--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-16).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-16).xlsx
@@ -915,66 +915,66 @@
   </si>
   <si>
     <t>215
-168</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>R$ 1.608.942,08</t>
-  </si>
-  <si>
-    <t>R$ 8.840,34
-R$ 9.097,46</t>
-  </si>
-  <si>
-    <t>(0.5%)
-2.4%</t>
-  </si>
-  <si>
-    <t>94.0</t>
+171</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>R$ 1.631.499,58</t>
+  </si>
+  <si>
+    <t>R$ 8.818,92
+R$ 9.069,77</t>
+  </si>
+  <si>
+    <t>(0.6%)
+2.3%</t>
+  </si>
+  <si>
+    <t>93.8</t>
   </si>
   <si>
     <t>(3.1%)</t>
   </si>
   <si>
-    <t>(47.6%)</t>
-  </si>
-  <si>
-    <t>(87.8%)</t>
-  </si>
-  <si>
-    <t>2.9%</t>
+    <t>(46.3%)</t>
+  </si>
+  <si>
+    <t>(86.3%)</t>
+  </si>
+  <si>
+    <t>3.0%</t>
   </si>
   <si>
     <t>0.7%</t>
   </si>
   <si>
-    <t>28.8</t>
-  </si>
-  <si>
-    <t>59.5%</t>
-  </si>
-  <si>
-    <t>13.1%</t>
+    <t>28.9</t>
+  </si>
+  <si>
+    <t>59.6%</t>
+  </si>
+  <si>
+    <t>13.3%</t>
   </si>
   <si>
     <t>6.2</t>
   </si>
   <si>
-    <t>7.6</t>
-  </si>
-  <si>
-    <t>13.7</t>
+    <t>7.7</t>
+  </si>
+  <si>
+    <t>14.1</t>
   </si>
   <si>
     <t>20.5</t>
   </si>
   <si>
-    <t>66.6%</t>
-  </si>
-  <si>
-    <t>-R$ 37.959,50</t>
+    <t>66.4%</t>
+  </si>
+  <si>
+    <t>-R$ 38.433,40</t>
   </si>
   <si>
     <t>2.94</t>
@@ -3924,7 +3924,7 @@
         <v>0.0078982894597485285</v>
       </c>
       <c r="W20" s="6">
-        <v>-0.0086939658965978651</v>
+        <v>-0.0085303753780855349</v>
       </c>
       <c r="X20" s="8">
         <v>31.04880071942446</v>
@@ -4836,7 +4836,7 @@
         <v>0</v>
       </c>
       <c r="AH27" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI27" s="11"/>
       <c r="AJ27" s="13">
@@ -5476,7 +5476,7 @@
         <v>4.0845313725490202</v>
       </c>
       <c r="AC32" s="8">
-        <v>6.8372570000000001</v>
+        <v>6.8085560000000003</v>
       </c>
       <c r="AD32" s="8">
         <v>12.770261437908497</v>
@@ -6709,7 +6709,7 @@
         <v>19579</v>
       </c>
       <c r="B42" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C42" s="4">
         <v>44</v>
@@ -6745,25 +6745,61 @@
       <c t="s" r="N42" s="4">
         <v>52</v>
       </c>
-      <c r="O42" s="5"/>
-      <c r="P42" s="5"/>
-      <c r="Q42" s="6"/>
-      <c r="R42" s="7"/>
-      <c r="S42" s="6"/>
-      <c r="T42" s="6"/>
-      <c r="U42" s="6"/>
-      <c r="V42" s="6"/>
-      <c r="W42" s="6"/>
-      <c r="X42" s="8"/>
-      <c r="Y42" s="6"/>
-      <c r="Z42" s="6"/>
-      <c r="AA42" s="8"/>
-      <c r="AB42" s="8"/>
-      <c r="AC42" s="8"/>
-      <c r="AD42" s="8"/>
-      <c r="AE42" s="6"/>
+      <c r="O42" s="5">
+        <v>9300.9500000000007</v>
+      </c>
+      <c r="P42" s="5">
+        <v>9300.9500000000007</v>
+      </c>
+      <c r="Q42" s="6">
+        <v>-0.01976603256573739</v>
+      </c>
+      <c r="R42" s="7">
+        <v>89</v>
+      </c>
+      <c r="S42" s="6">
+        <v>-0.053191489361702149</v>
+      </c>
+      <c r="T42" s="6">
+        <v>0.95678933872346372</v>
+      </c>
+      <c r="U42" s="6">
+        <v>0.6458297055677108</v>
+      </c>
+      <c r="V42" s="6">
+        <v>0.050186701358463377</v>
+      </c>
+      <c r="W42" s="6">
+        <v>0.02339696482617367</v>
+      </c>
+      <c r="X42" s="8">
+        <v>45.232527419354845</v>
+      </c>
+      <c r="Y42" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="Z42" s="6">
+        <v>0.56451612903225812</v>
+      </c>
+      <c r="AA42" s="8">
+        <v>9.0760540229885063</v>
+      </c>
+      <c r="AB42" s="8">
+        <v>17.965322580645161</v>
+      </c>
+      <c r="AC42" s="8">
+        <v>28.060213999999998</v>
+      </c>
+      <c r="AD42" s="8">
+        <v>34.991666129032254</v>
+      </c>
+      <c r="AE42" s="6">
+        <v>0.30645161290322581</v>
+      </c>
       <c r="AF42" s="9"/>
-      <c r="AG42" s="5"/>
+      <c r="AG42" s="5">
+        <v>0</v>
+      </c>
       <c r="AH42" s="10">
         <v>3</v>
       </c>
@@ -8148,7 +8184,9 @@
       <c r="AB53" s="8">
         <v>6.7553191489361701</v>
       </c>
-      <c r="AC53" s="8"/>
+      <c r="AC53" s="8">
+        <v>11.620678</v>
+      </c>
       <c r="AD53" s="8">
         <v>18.087589361702129</v>
       </c>
@@ -12076,7 +12114,7 @@
         <v>19687</v>
       </c>
       <c r="B85" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C85" s="4">
         <v>44</v>
@@ -12112,25 +12150,61 @@
       <c t="s" r="N85" s="4">
         <v>52</v>
       </c>
-      <c r="O85" s="5"/>
-      <c r="P85" s="5"/>
-      <c r="Q85" s="6"/>
-      <c r="R85" s="7"/>
-      <c r="S85" s="6"/>
-      <c r="T85" s="6"/>
-      <c r="U85" s="6"/>
-      <c r="V85" s="6"/>
-      <c r="W85" s="6"/>
-      <c r="X85" s="8"/>
-      <c r="Y85" s="6"/>
-      <c r="Z85" s="6"/>
-      <c r="AA85" s="8"/>
-      <c r="AB85" s="8"/>
-      <c r="AC85" s="8"/>
-      <c r="AD85" s="8"/>
-      <c r="AE85" s="6"/>
+      <c r="O85" s="5">
+        <v>3859.4000000000001</v>
+      </c>
+      <c r="P85" s="5">
+        <v>3859.4000000000001</v>
+      </c>
+      <c r="Q85" s="6">
+        <v>-0.041328636934954255</v>
+      </c>
+      <c r="R85" s="7">
+        <v>57</v>
+      </c>
+      <c r="S85" s="6">
+        <v>0.23913043478260865</v>
+      </c>
+      <c r="T85" s="6">
+        <v>0</v>
+      </c>
+      <c r="U85" s="6">
+        <v>-0.28380318184173703</v>
+      </c>
+      <c r="V85" s="6">
+        <v>0.020855962066642482</v>
+      </c>
+      <c r="W85" s="6">
+        <v>0.010012307612582266</v>
+      </c>
+      <c r="X85" s="8">
+        <v>31.875</v>
+      </c>
+      <c r="Y85" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z85" s="6">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="AA85" s="8">
+        <v>6.2361780487804879</v>
+      </c>
+      <c r="AB85" s="8">
+        <v>12.637499999999999</v>
+      </c>
+      <c r="AC85" s="8">
+        <v>19.359722000000001</v>
+      </c>
+      <c r="AD85" s="8">
+        <v>20.366666666666667</v>
+      </c>
+      <c r="AE85" s="6">
+        <v>0.58333333333333337</v>
+      </c>
       <c r="AF85" s="9"/>
-      <c r="AG85" s="5"/>
+      <c r="AG85" s="5">
+        <v>-248.19999999999999</v>
+      </c>
       <c r="AH85" s="10">
         <v>3</v>
       </c>
@@ -14144,7 +14218,7 @@
         <v>-30.5</v>
       </c>
       <c r="AH101" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI101" s="11"/>
       <c r="AJ101" s="13">
@@ -14261,7 +14335,9 @@
       <c r="AB102" s="8">
         <v>20.215277777777779</v>
       </c>
-      <c r="AC102" s="8"/>
+      <c r="AC102" s="8">
+        <v>31.200548000000001</v>
+      </c>
       <c r="AD102" s="8">
         <v>34.493749999999999</v>
       </c>
@@ -15943,7 +16019,9 @@
       <c r="Z116" s="6"/>
       <c r="AA116" s="8"/>
       <c r="AB116" s="8"/>
-      <c r="AC116" s="8"/>
+      <c r="AC116" s="8">
+        <v>13.438689999999999</v>
+      </c>
       <c r="AD116" s="8"/>
       <c r="AE116" s="6"/>
       <c r="AF116" s="9"/>
@@ -19811,7 +19889,9 @@
       <c r="AB146" s="8">
         <v>23.98764396551724</v>
       </c>
-      <c r="AC146" s="8"/>
+      <c r="AC146" s="8">
+        <v>40.287785</v>
+      </c>
       <c r="AD146" s="8">
         <v>46.038649137931031</v>
       </c>
@@ -20047,16 +20127,16 @@
         <v>0.12903225806451624</v>
       </c>
       <c r="T148" s="6">
-        <v>0</v>
+        <v>0.0045694800145937766</v>
       </c>
       <c r="U148" s="6">
-        <v>-0.30869122238588265</v>
+        <v>-0.30412174237128886</v>
       </c>
       <c r="V148" s="6">
         <v>0.020955920939427972</v>
       </c>
       <c r="W148" s="6">
-        <v>0.00038469309872861358</v>
+        <v>0.0053140196644716501</v>
       </c>
       <c r="X148" s="8">
         <v>38.798222000000003</v>
@@ -21715,7 +21795,7 @@
         <v>19872</v>
       </c>
       <c r="B162" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C162" s="4">
         <v>44</v>
@@ -21751,25 +21831,61 @@
       <c t="s" r="N162" s="4">
         <v>52</v>
       </c>
-      <c r="O162" s="5"/>
-      <c r="P162" s="5"/>
-      <c r="Q162" s="6"/>
-      <c r="R162" s="7"/>
-      <c r="S162" s="6"/>
-      <c r="T162" s="6"/>
-      <c r="U162" s="6"/>
-      <c r="V162" s="6"/>
-      <c r="W162" s="6"/>
-      <c r="X162" s="8"/>
-      <c r="Y162" s="6"/>
-      <c r="Z162" s="6"/>
-      <c r="AA162" s="8"/>
-      <c r="AB162" s="8"/>
-      <c r="AC162" s="8"/>
-      <c r="AD162" s="8"/>
-      <c r="AE162" s="6"/>
+      <c r="O162" s="5">
+        <v>9397.1499999999996</v>
+      </c>
+      <c r="P162" s="5">
+        <v>9397.1499999999996</v>
+      </c>
+      <c r="Q162" s="6">
+        <v>-0.1050384473993482</v>
+      </c>
+      <c r="R162" s="7">
+        <v>100</v>
+      </c>
+      <c r="S162" s="6">
+        <v>-0.14529914529914534</v>
+      </c>
+      <c r="T162" s="6">
+        <v>0.30953285836663247</v>
+      </c>
+      <c r="U162" s="6">
+        <v>0.032317958104318867</v>
+      </c>
+      <c r="V162" s="6">
+        <v>0.04534135349547469</v>
+      </c>
+      <c r="W162" s="6">
+        <v>0.034838169019330331</v>
+      </c>
+      <c r="X162" s="8">
+        <v>26.655405405405407</v>
+      </c>
+      <c r="Y162" s="6">
+        <v>0.78378378378378377</v>
+      </c>
+      <c r="Z162" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA162" s="8">
+        <v>7.5370563829787232</v>
+      </c>
+      <c r="AB162" s="8">
+        <v>1.8792783783783782</v>
+      </c>
+      <c r="AC162" s="8">
+        <v>10.225647</v>
+      </c>
+      <c r="AD162" s="8">
+        <v>18.100899999999999</v>
+      </c>
+      <c r="AE162" s="6">
+        <v>0.7567567567567568</v>
+      </c>
       <c r="AF162" s="9"/>
-      <c r="AG162" s="5"/>
+      <c r="AG162" s="5">
+        <v>-225.69999999999999</v>
+      </c>
       <c r="AH162" s="10">
         <v>2</v>
       </c>
@@ -21888,7 +22004,9 @@
       <c r="AB163" s="8">
         <v>6.6968531468531465</v>
       </c>
-      <c r="AC163" s="8"/>
+      <c r="AC163" s="8">
+        <v>11.651268</v>
+      </c>
       <c r="AD163" s="8">
         <v>18.956666666666667</v>
       </c>
@@ -24608,7 +24726,7 @@
         <v>19923</v>
       </c>
       <c r="B185" s="3">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c t="s" r="C185" s="4">
         <v>44</v>
@@ -25579,7 +25697,7 @@
         <v>-54.799999999999997</v>
       </c>
       <c r="AH192" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI192" s="11"/>
       <c r="AJ192" s="13">
@@ -26890,7 +27008,7 @@
         <v>19957</v>
       </c>
       <c r="B203" s="3">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c t="s" r="C203" s="4">
         <v>44</v>

--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-16).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-16).xlsx
@@ -915,33 +915,33 @@
   </si>
   <si>
     <t>215
-171</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>R$ 1.631.499,58</t>
-  </si>
-  <si>
-    <t>R$ 8.818,92
-R$ 9.069,77</t>
-  </si>
-  <si>
-    <t>(0.6%)
+176</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>R$ 1.678.131,84</t>
+  </si>
+  <si>
+    <t>R$ 8.832,27
+R$ 9.077,06</t>
+  </si>
+  <si>
+    <t>0.0%
 2.3%</t>
   </si>
   <si>
-    <t>93.8</t>
-  </si>
-  <si>
-    <t>(3.1%)</t>
-  </si>
-  <si>
-    <t>(46.3%)</t>
-  </si>
-  <si>
-    <t>(86.3%)</t>
+    <t>93.7</t>
+  </si>
+  <si>
+    <t>(2.7%)</t>
+  </si>
+  <si>
+    <t>(43.8%)</t>
+  </si>
+  <si>
+    <t>(83.5%)</t>
   </si>
   <si>
     <t>3.0%</t>
@@ -953,16 +953,16 @@
     <t>28.9</t>
   </si>
   <si>
-    <t>59.6%</t>
+    <t>59.8%</t>
   </si>
   <si>
     <t>13.3%</t>
   </si>
   <si>
-    <t>6.2</t>
-  </si>
-  <si>
-    <t>7.7</t>
+    <t>6.3</t>
+  </si>
+  <si>
+    <t>7.5</t>
   </si>
   <si>
     <t>14.1</t>
@@ -974,7 +974,7 @@
     <t>66.4%</t>
   </si>
   <si>
-    <t>-R$ 38.433,40</t>
+    <t>-R$ 38.520,15</t>
   </si>
   <si>
     <t>2.94</t>
@@ -1414,7 +1414,7 @@
     <col min="14" max="14" width="12.14" customWidth="1"/>
     <col min="15" max="15" width="15.29" customWidth="1"/>
     <col min="16" max="16" width="16" customWidth="1"/>
-    <col min="17" max="17" width="6.86" customWidth="1"/>
+    <col min="17" max="17" width="7.71" customWidth="1"/>
     <col min="18" max="18" width="10.14" customWidth="1"/>
     <col min="19" max="19" width="13.71" customWidth="1"/>
     <col min="20" max="20" width="12" customWidth="1"/>
@@ -2069,7 +2069,7 @@
         <v>19507</v>
       </c>
       <c r="B6" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C6" s="4">
         <v>44</v>
@@ -2105,25 +2105,61 @@
       <c t="s" r="N6" s="4">
         <v>52</v>
       </c>
-      <c r="O6" s="5"/>
-      <c r="P6" s="5"/>
-      <c r="Q6" s="6"/>
-      <c r="R6" s="7"/>
-      <c r="S6" s="6"/>
-      <c r="T6" s="6"/>
-      <c r="U6" s="6"/>
-      <c r="V6" s="6"/>
-      <c r="W6" s="6"/>
-      <c r="X6" s="8"/>
-      <c r="Y6" s="6"/>
-      <c r="Z6" s="6"/>
-      <c r="AA6" s="8"/>
-      <c r="AB6" s="8"/>
-      <c r="AC6" s="8"/>
-      <c r="AD6" s="8"/>
-      <c r="AE6" s="6"/>
+      <c r="O6" s="5">
+        <v>15289.34</v>
+      </c>
+      <c r="P6" s="5">
+        <v>15289.34</v>
+      </c>
+      <c r="Q6" s="6">
+        <v>0.23056207483814473</v>
+      </c>
+      <c r="R6" s="7">
+        <v>145</v>
+      </c>
+      <c r="S6" s="6">
+        <v>0.082089552238805874</v>
+      </c>
+      <c r="T6" s="6">
+        <v>0.26782652488596631</v>
+      </c>
+      <c r="U6" s="6">
+        <v>0.015238774204772737</v>
+      </c>
+      <c r="V6" s="6">
+        <v>0.030332113747225189</v>
+      </c>
+      <c r="W6" s="6">
+        <v>0.0072317052273021595</v>
+      </c>
+      <c r="X6" s="8">
+        <v>24.819515384615386</v>
+      </c>
+      <c r="Y6" s="6">
+        <v>0.93162393162393164</v>
+      </c>
+      <c r="Z6" s="6">
+        <v>0.0085470085470085479</v>
+      </c>
+      <c r="AA6" s="8">
+        <v>9.7917808219178077</v>
+      </c>
+      <c r="AB6" s="8">
+        <v>1.9975149122807019</v>
+      </c>
+      <c r="AC6" s="8">
+        <v>11.827598</v>
+      </c>
+      <c r="AD6" s="8">
+        <v>18.661965811965811</v>
+      </c>
+      <c r="AE6" s="6">
+        <v>0.78632478632478631</v>
+      </c>
       <c r="AF6" s="9"/>
-      <c r="AG6" s="5"/>
+      <c r="AG6" s="5">
+        <v>-75.5</v>
+      </c>
       <c r="AH6" s="10">
         <v>5</v>
       </c>
@@ -2740,10 +2776,10 @@
         <v>0.10294117647058831</v>
       </c>
       <c r="T11" s="6">
-        <v>0.10022800516488212</v>
+        <v>0.10886178496148233</v>
       </c>
       <c r="U11" s="6">
-        <v>-0.15833801810075782</v>
+        <v>-0.14970423830415758</v>
       </c>
       <c r="V11" s="6">
         <v>0.015366559873694724</v>
@@ -5709,10 +5745,10 @@
         <v>0.54166666666666674</v>
       </c>
       <c r="T34" s="6">
-        <v>0.23245711536183386</v>
+        <v>0.45981660531410223</v>
       </c>
       <c r="U34" s="6">
-        <v>-0.10729617761579596</v>
+        <v>0.12021151400188859</v>
       </c>
       <c r="V34" s="6">
         <v>0.040669413272531652</v>
@@ -7882,7 +7918,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>44</v>
@@ -7918,11 +7954,21 @@
       <c t="s" r="N51" s="4">
         <v>52</v>
       </c>
-      <c r="O51" s="5"/>
-      <c r="P51" s="5"/>
-      <c r="Q51" s="6"/>
-      <c r="R51" s="7"/>
-      <c r="S51" s="6"/>
+      <c r="O51" s="5">
+        <v>0</v>
+      </c>
+      <c r="P51" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="6">
+        <v>-1</v>
+      </c>
+      <c r="R51" s="7">
+        <v>0</v>
+      </c>
+      <c r="S51" s="6">
+        <v>-1</v>
+      </c>
       <c r="T51" s="6"/>
       <c r="U51" s="6"/>
       <c r="V51" s="6"/>
@@ -7936,7 +7982,9 @@
       <c r="AD51" s="8"/>
       <c r="AE51" s="6"/>
       <c r="AF51" s="9"/>
-      <c r="AG51" s="5"/>
+      <c r="AG51" s="5">
+        <v>0</v>
+      </c>
       <c r="AH51" s="10">
         <v>2</v>
       </c>
@@ -8809,7 +8857,9 @@
       <c r="Z58" s="6"/>
       <c r="AA58" s="8"/>
       <c r="AB58" s="8"/>
-      <c r="AC58" s="8"/>
+      <c r="AC58" s="8">
+        <v>11.92205</v>
+      </c>
       <c r="AD58" s="8"/>
       <c r="AE58" s="6"/>
       <c r="AF58" s="9"/>
@@ -20468,7 +20518,7 @@
         <v>19821</v>
       </c>
       <c r="B151" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C151" s="4">
         <v>44</v>
@@ -20504,25 +20554,61 @@
       <c t="s" r="N151" s="4">
         <v>52</v>
       </c>
-      <c r="O151" s="5"/>
-      <c r="P151" s="5"/>
-      <c r="Q151" s="6"/>
-      <c r="R151" s="7"/>
-      <c r="S151" s="6"/>
-      <c r="T151" s="6"/>
-      <c r="U151" s="6"/>
-      <c r="V151" s="6"/>
-      <c r="W151" s="6"/>
-      <c r="X151" s="8"/>
-      <c r="Y151" s="6"/>
-      <c r="Z151" s="6"/>
-      <c r="AA151" s="8"/>
-      <c r="AB151" s="8"/>
-      <c r="AC151" s="8"/>
-      <c r="AD151" s="8"/>
-      <c r="AE151" s="6"/>
+      <c r="O151" s="5">
+        <v>7175.1199999999999</v>
+      </c>
+      <c r="P151" s="5">
+        <v>7175.1199999999999</v>
+      </c>
+      <c r="Q151" s="6">
+        <v>-0.16226948201682445</v>
+      </c>
+      <c r="R151" s="7">
+        <v>77</v>
+      </c>
+      <c r="S151" s="6">
+        <v>-0.1348314606741573</v>
+      </c>
+      <c r="T151" s="6">
+        <v>0.30062677697376489</v>
+      </c>
+      <c r="U151" s="6">
+        <v>-0.0075840961544894024</v>
+      </c>
+      <c r="V151" s="6">
+        <v>0.034702834238312393</v>
+      </c>
+      <c r="W151" s="6">
+        <v>0.011677435359966105</v>
+      </c>
+      <c r="X151" s="8">
+        <v>24.364062499999999</v>
+      </c>
+      <c r="Y151" s="6">
+        <v>0.46875</v>
+      </c>
+      <c r="Z151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA151" s="8">
+        <v>5.836363636363636</v>
+      </c>
+      <c r="AB151" s="8">
+        <v>2.0888015625</v>
+      </c>
+      <c r="AC151" s="8">
+        <v>8.0936730000000008</v>
+      </c>
+      <c r="AD151" s="8">
+        <v>15.017707812499999</v>
+      </c>
+      <c r="AE151" s="6">
+        <v>0.90625</v>
+      </c>
       <c r="AF151" s="9"/>
-      <c r="AG151" s="5"/>
+      <c r="AG151" s="5">
+        <v>0</v>
+      </c>
       <c r="AH151" s="10">
         <v>5</v>
       </c>
@@ -21218,7 +21304,7 @@
         <v>19855</v>
       </c>
       <c r="B157" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C157" s="4">
         <v>44</v>
@@ -21254,25 +21340,61 @@
       <c t="s" r="N157" s="4">
         <v>52</v>
       </c>
-      <c r="O157" s="5"/>
-      <c r="P157" s="5"/>
-      <c r="Q157" s="6"/>
-      <c r="R157" s="7"/>
-      <c r="S157" s="6"/>
-      <c r="T157" s="6"/>
-      <c r="U157" s="6"/>
-      <c r="V157" s="6"/>
-      <c r="W157" s="6"/>
-      <c r="X157" s="8"/>
-      <c r="Y157" s="6"/>
-      <c r="Z157" s="6"/>
-      <c r="AA157" s="8"/>
-      <c r="AB157" s="8"/>
-      <c r="AC157" s="8"/>
-      <c r="AD157" s="8"/>
-      <c r="AE157" s="6"/>
+      <c r="O157" s="5">
+        <v>7125.9099999999999</v>
+      </c>
+      <c r="P157" s="5">
+        <v>7125.9099999999999</v>
+      </c>
+      <c r="Q157" s="6">
+        <v>0.012522414738738608</v>
+      </c>
+      <c r="R157" s="7">
+        <v>69</v>
+      </c>
+      <c r="S157" s="6">
+        <v>-0.028169014084507005</v>
+      </c>
+      <c r="T157" s="6">
+        <v>0.31634373715076392</v>
+      </c>
+      <c r="U157" s="6">
+        <v>0.024072293924565426</v>
+      </c>
+      <c r="V157" s="6">
+        <v>0.038448142061855962</v>
+      </c>
+      <c r="W157" s="6">
+        <v>0.019403556879051237</v>
+      </c>
+      <c r="X157" s="8">
+        <v>27.581285964912279</v>
+      </c>
+      <c r="Y157" s="6">
+        <v>0.68421052631578949</v>
+      </c>
+      <c r="Z157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA157" s="8">
+        <v>7.8401955882352938</v>
+      </c>
+      <c r="AB157" s="8">
+        <v>3.450584210526316</v>
+      </c>
+      <c r="AC157" s="8">
+        <v>11.726022</v>
+      </c>
+      <c r="AD157" s="8">
+        <v>18.675731578947367</v>
+      </c>
+      <c r="AE157" s="6">
+        <v>0.66666666666666663</v>
+      </c>
       <c r="AF157" s="9"/>
-      <c r="AG157" s="5"/>
+      <c r="AG157" s="5">
+        <v>0</v>
+      </c>
       <c r="AH157" s="10">
         <v>4</v>
       </c>
@@ -21313,7 +21435,7 @@
         <v>19859</v>
       </c>
       <c r="B158" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C158" s="4">
         <v>44</v>
@@ -21349,25 +21471,61 @@
       <c t="s" r="N158" s="4">
         <v>52</v>
       </c>
-      <c r="O158" s="5"/>
-      <c r="P158" s="5"/>
-      <c r="Q158" s="6"/>
-      <c r="R158" s="7"/>
-      <c r="S158" s="6"/>
-      <c r="T158" s="6"/>
-      <c r="U158" s="6"/>
-      <c r="V158" s="6"/>
-      <c r="W158" s="6"/>
-      <c r="X158" s="8"/>
-      <c r="Y158" s="6"/>
-      <c r="Z158" s="6"/>
-      <c r="AA158" s="8"/>
-      <c r="AB158" s="8"/>
-      <c r="AC158" s="8"/>
-      <c r="AD158" s="8"/>
-      <c r="AE158" s="6"/>
+      <c r="O158" s="5">
+        <v>7934.8999999999996</v>
+      </c>
+      <c r="P158" s="5">
+        <v>7934.8999999999996</v>
+      </c>
+      <c r="Q158" s="6">
+        <v>-0.1556694822012672</v>
+      </c>
+      <c r="R158" s="7">
+        <v>77</v>
+      </c>
+      <c r="S158" s="6">
+        <v>-0.25242718446601942</v>
+      </c>
+      <c r="T158" s="6">
+        <v>0.38894138552470731</v>
+      </c>
+      <c r="U158" s="6">
+        <v>0.11999533705528741</v>
+      </c>
+      <c r="V158" s="6">
+        <v>0.027105193512205573</v>
+      </c>
+      <c r="W158" s="6">
+        <v>0.0071389683549887206</v>
+      </c>
+      <c r="X158" s="8">
+        <v>33.224074603174607</v>
+      </c>
+      <c r="Y158" s="6">
+        <v>0.77777777777777779</v>
+      </c>
+      <c r="Z158" s="6">
+        <v>0.25396825396825395</v>
+      </c>
+      <c r="AA158" s="8">
+        <v>7.8982688311688314</v>
+      </c>
+      <c r="AB158" s="8">
+        <v>4.8053758064516128</v>
+      </c>
+      <c r="AC158" s="8">
+        <v>13.086857</v>
+      </c>
+      <c r="AD158" s="8">
+        <v>19.94126984126984</v>
+      </c>
+      <c r="AE158" s="6">
+        <v>0.34920634920634919</v>
+      </c>
       <c r="AF158" s="9"/>
-      <c r="AG158" s="5"/>
+      <c r="AG158" s="5">
+        <v>0</v>
+      </c>
       <c r="AH158" s="10">
         <v>2</v>
       </c>
@@ -22188,7 +22346,7 @@
         <v>19877</v>
       </c>
       <c r="B165" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C165" s="4">
         <v>44</v>
@@ -22224,25 +22382,61 @@
       <c t="s" r="N165" s="4">
         <v>52</v>
       </c>
-      <c r="O165" s="5"/>
-      <c r="P165" s="5"/>
-      <c r="Q165" s="6"/>
-      <c r="R165" s="7"/>
-      <c r="S165" s="6"/>
-      <c r="T165" s="6"/>
-      <c r="U165" s="6"/>
-      <c r="V165" s="6"/>
-      <c r="W165" s="6"/>
-      <c r="X165" s="8"/>
-      <c r="Y165" s="6"/>
-      <c r="Z165" s="6"/>
-      <c r="AA165" s="8"/>
-      <c r="AB165" s="8"/>
-      <c r="AC165" s="8"/>
-      <c r="AD165" s="8"/>
-      <c r="AE165" s="6"/>
+      <c r="O165" s="5">
+        <v>9106.9899999999998</v>
+      </c>
+      <c r="P165" s="5">
+        <v>9106.9899999999998</v>
+      </c>
+      <c r="Q165" s="6">
+        <v>0.097807035519948959</v>
+      </c>
+      <c r="R165" s="7">
+        <v>98</v>
+      </c>
+      <c r="S165" s="6">
+        <v>0.010309278350515427</v>
+      </c>
+      <c r="T165" s="6">
+        <v>0.26301847262377581</v>
+      </c>
+      <c r="U165" s="6">
+        <v>-0.015802520920743298</v>
+      </c>
+      <c r="V165" s="6">
+        <v>0.019152486167218808</v>
+      </c>
+      <c r="W165" s="6">
+        <v>-0.0022629320994093549</v>
+      </c>
+      <c r="X165" s="8">
+        <v>38.257618571428573</v>
+      </c>
+      <c r="Y165" s="6">
+        <v>0.34285714285714286</v>
+      </c>
+      <c r="Z165" s="6">
+        <v>0.42857142857142855</v>
+      </c>
+      <c r="AA165" s="8">
+        <v>12.884375</v>
+      </c>
+      <c r="AB165" s="8">
+        <v>5.1123814285714282</v>
+      </c>
+      <c r="AC165" s="8">
+        <v>20.482098000000001</v>
+      </c>
+      <c r="AD165" s="8">
+        <v>27.520952857142856</v>
+      </c>
+      <c r="AE165" s="6">
+        <v>0.51428571428571423</v>
+      </c>
       <c r="AF165" s="9"/>
-      <c r="AG165" s="5"/>
+      <c r="AG165" s="5">
+        <v>-11.25</v>
+      </c>
       <c r="AH165" s="10">
         <v>3</v>
       </c>
